--- a/Tables/ENEMY_DATA.xlsx
+++ b/Tables/ENEMY_DATA.xlsx
@@ -734,32 +734,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Label</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">EnemyKey</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필드</t>
+          <t xml:space="preserve">한글 라벨</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">수치</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">한글 라벨</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">수치</t>
         </is>
@@ -768,120 +768,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t xml:space="preserve">보병</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근접</t>
+        </is>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t xml:space="preserve">포격</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원거리</t>
+        </is>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t xml:space="preserve">장갑</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">길막</t>
+        </is>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t xml:space="preserve">강적</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="B6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">근접</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">원거리</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">길막</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">보스</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="E6">
         <v>4</v>
       </c>
     </row>
@@ -895,133 +847,69 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">ENEMY_DATA 테이블 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t xml:space="preserve">INDEX</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FieldName</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DataType</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Example</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Description</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번호</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">필드명</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">간략 설명</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 타입</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">데이터 예시</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">필드 설명/값</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고(근거)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dev_Index</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개발용 번호</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">컨버팅 제외(Dev_ 접두)</t>
+          <t xml:space="preserve">필드 설명 / 값</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">사람이 표를 읽을 때만 쓴다</t>
+          <t xml:space="preserve">비고</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dev_Desc</t>
+          <t xml:space="preserve">Dev_Index</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">개발용 설명</t>
+          <t xml:space="preserve">개발용 번호</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보병(infantry)</t>
-        </is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1030,60 +918,62 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">json role 문장이 여기로 온다</t>
+          <t xml:space="preserve">사람이 표를 읽을 때만 쓴다</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Dev_Desc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">고유 번호</t>
+          <t xml:space="preserve">개발용 설명</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>1</v>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보병(infantry)</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1부터</t>
+          <t xml:space="preserve">컨버팅 제외(Dev_ 접두)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">행 식별</t>
+          <t xml:space="preserve">json role 문장이 여기로 온다</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyKey</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">적 종류</t>
+          <t xml:space="preserve">고유 번호</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">enum</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E6">
@@ -1091,161 +981,161 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">보병1 포격2 장갑3 강적4</t>
+          <t xml:space="preserve">1부터</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Designer_Data 참조</t>
+          <t xml:space="preserve">행 식별</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TID_Name</t>
+          <t xml:space="preserve">EnemyKey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">표시 이름</t>
+          <t xml:space="preserve">적 종류</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보병</t>
-        </is>
+          <t xml:space="preserve">enum</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">화면에 보이는 한글 이름</t>
+          <t xml:space="preserve">보병1 포격2 장갑3 강적4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnemyDefinition.displayName</t>
+          <t xml:space="preserve">Designer_Data 참조</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Role</t>
+          <t xml:space="preserve">TID_Name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">역할</t>
+          <t xml:space="preserve">표시 이름</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">enum</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>1</v>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보병</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">근접1 원거리2 길막3 보스4</t>
+          <t xml:space="preserve">화면에 보이는 한글 이름</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">json role 문장 → enum</t>
+          <t xml:space="preserve">EnemyDefinition.displayName</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atk</t>
+          <t xml:space="preserve">Role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격력</t>
+          <t xml:space="preserve">역할</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t xml:space="preserve">enum</t>
         </is>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 대의 피해</t>
+          <t xml:space="preserve">근접1 원거리2 길막3 보스4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enemy_*.asset 의 atk</t>
+          <t xml:space="preserve">json role 문장 → enum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MoveSpeed</t>
+          <t xml:space="preserve">Atk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 속도</t>
+          <t xml:space="preserve">공격력</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t xml:space="preserve">int</t>
         </is>
       </c>
       <c r="E10">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유닛/초</t>
+          <t xml:space="preserve">한 대의 피해</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">**자산이 0 이라 CombatTuning.enemyMoveSpeedTbd 폴백** · ⚠️ 가정 · ⚠️⚠️ 자산은 **1.5** 인데 C# 기본값은 1.2 다 — **자산이 이긴다.** 1.2 를 적은 글은 낡았다</t>
+          <t xml:space="preserve">Enemy_*.asset 의 atk</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AttackRange</t>
+          <t xml:space="preserve">MoveSpeed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">사거리</t>
+          <t xml:space="preserve">이동 속도</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1254,31 +1144,31 @@
         </is>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">표면에서 이만큼 떨어져 때린다</t>
+          <t xml:space="preserve">유닛/초</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">보병·장갑·강적 = CombatTuning 폴백(⚠️ 가정) · **포격만 EnemyAttackRule.ArtilleryRangeAssumed = 7**(⚠️ 가정 · 플랜 6~8 의 가운데)</t>
+          <t xml:space="preserve">**자산이 0 이라 CombatTuning.enemyMoveSpeedTbd 폴백** · ⚠️ 가정 · ⚠️⚠️ 자산은 **1.5** 인데 C# 기본값은 1.2 다 — **자산이 이긴다.** 1.2 를 적은 글은 낡았다</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">AttackInterval</t>
+          <t xml:space="preserve">AttackRange</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격 주기</t>
+          <t xml:space="preserve">사거리</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1291,27 +1181,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">초</t>
+          <t xml:space="preserve">표면에서 이만큼 떨어져 때린다</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">**자산이 0 이라 CombatTuning.enemyAttackIntervalTbd 폴백** · ⚠️ 가정 · ⚠️⚠️ 자산은 **1** 인데 C# 기본값은 1.5 다 — **자산이 이긴다**</t>
+          <t xml:space="preserve">보병·장갑·강적 = CombatTuning 폴백(⚠️ 가정) · **포격만 EnemyAttackRule.ArtilleryRangeAssumed = 7**(⚠️ 가정 · 플랜 6~8 의 가운데)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProjectileSpeed</t>
+          <t xml:space="preserve">AttackInterval</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">투사체 속도</t>
+          <t xml:space="preserve">공격 주기</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1320,115 +1210,148 @@
         </is>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 = 즉발(포탄이 없다)</t>
+          <t xml:space="preserve">초</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">포격만 EnemyAttackRule.ProjectileSpeedAssumed = **4.2**(✅ 사용자 확정 09-18 「지금 속도의 70%」) · 나머지 0</t>
+          <t xml:space="preserve">**자산이 0 이라 CombatTuning.enemyAttackIntervalTbd 폴백** · ⚠️ 가정 · ⚠️⚠️ 자산은 **1** 인데 C# 기본값은 1.5 다 — **자산이 이긴다**</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ViewScale</t>
+          <t xml:space="preserve">ProjectileSpeed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">그림 배율</t>
+          <t xml:space="preserve">투사체 속도</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t xml:space="preserve">float</t>
         </is>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">보스만 2</t>
+          <t xml:space="preserve">0 = 즉발(포탄이 없다)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ArtSpec.BossViewScale</t>
+          <t xml:space="preserve">포격만 EnemyAttackRule.ProjectileSpeedAssumed = **4.2**(✅ 사용자 확정 09-18 「지금 속도의 70%」) · 나머지 0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ArtKey</t>
+          <t xml:space="preserve">ViewScale</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">그림 키</t>
+          <t xml:space="preserve">그림 배율</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mob_infantry</t>
-        </is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">아트 자산 이름</t>
+          <t xml:space="preserve">보스만 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Art/Units 아래 폴더 이름</t>
+          <t xml:space="preserve">ArtSpec.BossViewScale</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ArtKey</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그림 키</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mob_infantry</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아트 자산 이름</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Art/Units 아래 폴더 이름</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">Confirmed</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">확정 여부</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">bool</t>
         </is>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">1=확정 0=가정</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">**넷 다 0** — Atk 은 자산 값이라 확정 플래그가 원래 없고, 나머지 넷은 가정 또는 폴백이다. ⚠️ ProjectileSpeed 4.2 **한 칸만 사용자 확정**이라 행 단위 플래그로는 못 적는다(설계 판정 자리)</t>
         </is>
